--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -813,4 +814,642 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.04614683745649018</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.03965818333686504</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.04104214294534529</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.01420652042548909</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.01365683206889537</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01373100104692136</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.01085601933721136</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.007017898928618846</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.02665343657367095</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.01267743353962203</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.009913008133272954</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.009738391673831242</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.02006068328455513</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.004461735706929786</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.004410008521096812</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.01541481617312002</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.003535401091680832</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.001591749082106121</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>85</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.01197492310245707</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.005088133816473335</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.004449168319416716</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01374783675731805</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002256925976307165</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0008366852171535812</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>115</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01198570397608023</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.003292069843093751</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.003283403237386312</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>130</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01427176658879148</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001930905376017969</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.001938429074627062</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.02116845598982309</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.002406856310956495</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.002408547847083268</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>200</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.01428911053000093</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.002051102086596742</v>
+      </c>
+      <c r="L13" t="n">
+        <v>66.96149338845495</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1452,4 +1453,458 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2441275614503411</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.01804390923965773</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3318.573703706419</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2233523299419176</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.007192398921708439</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.04785348242509953</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.815007036531767</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.03307535813742337</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.443007962940326</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.02079995353090425</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.002572379648999824</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.001180105538751635</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01374739747149079</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.00231686441845232</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0009007905817530963</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.01374783675731805</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.002256925976307165</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0008366852171535812</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.01385334082419831</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.002270446180293009</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.001526451211298812</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01404399246979438</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.00230558955959203</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.001004860347281073</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1907,4 +1908,688 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.1346706192307465</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.02009768746286485</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3390448964846217</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.06791457137205725</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.009924286368938615</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0002690693436433965</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.01507134336696936</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.002611524043962048</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0002350403568681885</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.01440049912145014</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.002214260370120215</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0003174891791367281</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01386529282169136</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.002212679948150371</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0006273990001168135</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0138034738359778</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.002233941843734203</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0006728458612157451</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.01375401865651327</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.002254195634022963</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0008581476176123962</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01374783675731805</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002256925976307165</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0008366852171535812</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01374289123504013</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.002259141662770683</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001509951101416929</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01374227305144871</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.002259420583010506</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.001466810960337382</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.01374177849292835</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.002259644032191491</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.002620293080557157</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0137417166746161</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.002259671982315889</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.002061295693291889</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.01374166722926873</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.002259694346026038</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.002786714281848602</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvector Angle" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2592,4 +2593,504 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.01335700222841297</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.01352644175409883</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0004024168698582322</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.01048816162810007</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.005105719193083707</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.3370340109191272</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.007711325299455729</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.002527382486210949</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.966654244228119</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.01076858025609895</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.002157056906031871</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.08894818749546601</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01374783675731805</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.002256925976307165</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0008366852171535812</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.01078137517808508</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.002160409292469587</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.01306639342036148</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.007719440997052573</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.00253324110059205</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0144796776495729</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01041647806250645</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.005112023088829798</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1455684592464005</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01335700231549708</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01352644175754828</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0004024168679831317</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1053,721 @@
         <v>250</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.623688242910298</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3140635614984055</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.704623031789381</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0006124652581860346</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.018640915367681e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.508667763571159</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6707539446020772</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.504054698992313</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.002448446982711516</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0001608945754518933</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0004865464430802528</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0003670540005042626</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.000805050769966753</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001752393535753072</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0007948095089925423</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.949948044676335e-05</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.748103679104261e-05</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.702696858959941e-05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.0002045546930276032</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.640780312653723e-05</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.001748218500927286</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0008351019856494985</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.002587253051075003</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.001371504348995245</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0002184003749611982</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>100</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.003267488543217715</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.002098176736158957</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.005557231655165387</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.001597915655565885</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0004263081982190849</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.03081441707636016</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.01875089411728562</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.04715704636047829</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.003775606067847548</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.001155545607336516</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>100</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.002227041551396673</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.001493593623675136</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.003460689420398171</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.004906133793054934</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.002434122525633349</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.000123956481290192</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7.486513973281101e-05</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.00020622832962076</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.0003239371098118227</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.335171693483948e-05</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>100</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.00312089907963579</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.001727128414176693</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.004244667223316411</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.001212085532557694</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0002343773817861423</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.01793931360676426</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.01155622708670305</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.0265050180283981</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.007988036233371076</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.003850897439898678</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.03009790512995858</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.01971136523212565</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.048382575692305</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.01737306314350917</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.001409668558579373</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>100</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0360552932480345</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.01042860002208441</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1090172163745386</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.201312968274578</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.05939004059058126</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1771,4 +1772,765 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.004407862406502483</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.002288358655221417</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.008840858770008016</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.01705065482664736</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.001426545646033015</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0009324976095187824</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0002521870814161335</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0007035805093563119</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0007659324554083469</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0001151634267693054</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.001664246283586746</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0006762894695129357</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.001897471017928401</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002126727633850578</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0003848228734983204</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0003226140943916415</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0001755587824198764</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0005459659036332014</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002242806695988975</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0003623331861819522</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.002375084997276936</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.001341468977552138</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.003401642403156228</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001608485647921043</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0004717176529333667</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0008355925928079285</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0004981952498028163</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.001319761651722078</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002527517654584699</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0006770304317894911</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0007242443825878908</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0005372746009762015</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.001116971726923114</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.003042993127280624</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0008854721739862015</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.03081441707636016</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01875089411728562</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.04715704636047829</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.003775606067847548</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.001155545607336516</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.003274446679907506</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001257004610870657</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.005930617915483585</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.003837329590368199</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.001542633021271662</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001450991362213679</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.00115906754936884</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.002559110426220815</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.004041601110841953</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.001838058924415625</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.003683629121668049</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.002114877044198662</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.006467576826553904</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.004986771273550517</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.00156118377353597</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.2757205314448e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.155242221175181e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9.719124058120243e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0009874137295753371</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6.955997389508706e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2533,4 +2534,545 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.001264338297676322</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.000598291902380732</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.001702368014235039</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.002918255641020551</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.001085251461534864</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.005513175132928112</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.002805180406844399</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.007683508443230147</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.002890190466700915</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.001113595642748026</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.012015186488003</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.005721897626508427</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.01528179371229674</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.003213193518888602</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001120915795301397</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.002888574609084168</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.001482967193326658</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.003512785113756703</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.003211977768614815</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001123248454120572</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.002530789150269719</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.001456285248150701</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.003888759159303017</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.003796406046603806</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.001154512708914342</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.03081441707636016</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.01875089411728562</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.04715704636047829</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.003775606067847548</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.001155545607336516</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.001751662493401455</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0009141120447867918</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.002468627525188493</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.003763348908819353</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.001155518687260387</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.001740411012315146</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.001028677298221576</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.002476583067619468</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.003755250870597138</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.00115516010602135</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3075,4 +3076,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.001421571513043673</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0007171538993499294</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.001618421550826797</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.03876173959770313</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01139947591467098</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0004064365422962919</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0004501643469999909</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0005891886574361607</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.01905394332789001</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.006219989345333854</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.000780631370686328</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0003440833491941301</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.001384298626238411</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.004489645315175039</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.002117973959834481</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0004593115705130065</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0004711146695956043</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0007660203517195945</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.003726573530116184</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001623529343431803</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.001366359504182846</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0006521843990942324</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.002111276942359047</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.003715741609710221</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.001242548565100713</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0009175740445478789</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0004839392840698322</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.00170437562867563</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.003747260465900126</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.001196532703850568</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.003163323504268659</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.002012957794352181</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.005283584886409307</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.003772458552077751</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.001160078260226388</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.03081441707636016</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01875089411728562</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.04715704636047829</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.003775606067847548</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.001155545607336516</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1081601888895338</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.05114902780303289</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1197391533354896</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.003778139350231413</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.001151923398189923</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.02248624174563441</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01140307034580057</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.02649698675167186</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.00377844852545195</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.001151470962065467</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.01147947660534735</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.006100538819578515</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.01407164559448058</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.003778703452496757</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.001151108925500595</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.01072884593647864</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.00572062245010102</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01317850147969638</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.003778725898939683</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.001151063695213861</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.01017282517464565</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.005439656977442414</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.01251710142236537</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.003778757652412423</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.001151027477046815</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvector Angle" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3892,4 +3893,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0025986769795181</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.001591666580549118</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.002415850110827087</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.003938306065090273</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.00686238901574376</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0008649621689966006</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0004371956968152341</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0008450854819949659</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.002838015352264245</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.003563430469943539</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.001091364320337333</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.001141764214900201</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.001402462648296746</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.00287748216868311</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.002050368944263148</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.000757771769306507</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0003179057070300901</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001220744947165254</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002897157502361414</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001454340147832822</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.03081441707636016</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.01875089411728562</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.04715704636047829</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.003775606067847548</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.001155545607336516</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0005271511421673184</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0003831222617652864</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.001458433441599174</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002660333898618972</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.001455289563844649</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0005676631642579366</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0002684833407620977</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0008770153718382317</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002315541690736667</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.002051643625521319</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0003636929573384388</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.000373015844098598</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.000532145459109655</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002778514118315423</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.003564827116120665</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.00259844982239669</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001591512496631809</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.002415634829492266</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.003938306085951808</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.006862389035228439</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B9DBE4-D714-458F-A1D2-54A1CC7FE61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" r:id="rId1"/>

--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dc858\Documents\Projects\RBF-FD-Elliptic\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B9DBE4-D714-458F-A1D2-54A1CC7FE61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2C81E6-76D6-498E-BBA4-9140700B5283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
+    <sheet name="Length Scale" sheetId="6" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="2" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="3" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="4" r:id="rId5"/>

--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dc858\Documents\Projects\RBF-FD-Elliptic\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2C81E6-76D6-498E-BBA4-9140700B5283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE0B6A93-925B-4E6A-8A5E-6961DA346B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,20 @@
     <sheet name="Eigenvalue Ratio" sheetId="4" r:id="rId5"/>
     <sheet name="Eigenvector Angle" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,4 +1057,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.179626898790588e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.171428763175451e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.166112822733087e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0002187893348946091</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.611737033860464e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.000104783552736798</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.156902261587953e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001558473100539263</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0008717819730463816</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5.063564871126853e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001006551181500133</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001176364420447257</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0002490467148599282</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0003634056682813025</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0002536704399067269</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.000712405578387069</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0007396865401333395</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001540084880312125</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002688181953544699</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.00152331711511153</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.89691808900435e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.717503706613038e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5.201603847288356e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0003705118685957132</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.870619668894504e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001049824975165592</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4.582547056279992e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0001321446202805261</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0008457970492372624</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7.237613559922223e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0002035220388556525</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.049508745097712e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0003093330458305907</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001588027163331729</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0001652446832776666</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001218181219691713</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001148098515540773</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002379375884136502</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001393029960979675</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0002711506010816133</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0004847512758444268</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0002531303653497078</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0007683685152512445</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002602097596998476</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0005632841426032619</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001239487076842849</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0009735141833182977</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.002342107891087334</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.005019508567102093</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.001908025982802578</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.000557172975070556</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0002703383230610874</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.001023004481311924</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.09750017168698832</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.001866562249107217</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.007233485546344731</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.003434647719553856</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01017963606804799</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8463647476164624</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01326947996089244</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.08349254847444021</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0399243605130933</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1389681340353868</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20.94554648612393</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2809492714903693</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.2081895916597358</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1659696294192916</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4000108653985406</v>
+      </c>
+      <c r="N15" t="n">
+        <v>141.6619834560552</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.854774645708974</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.211885834597845</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.004997699287952</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.712924088512576</v>
+      </c>
+      <c r="N16" t="n">
+        <v>229.9054243346873</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5.388465564437572</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1983,4 +1984,875 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.006362307085501524</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.002660440521986851</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.01139438104394147</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.05229784385068115</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.004265540789314286</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0009969829547843052</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0006375714449263311</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.001890089906757263</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.002789711415289275</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0004512215907371672</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0008540953327272524</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0005653986124530152</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.00150237466300982</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002894556203500542</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0008175100595433176</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0009017507242744157</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0007948058371895538</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001615248627973328</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.005819454185029826</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001627969040266676</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.001542182495001339</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.001147368186105807</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.002762518853011011</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.006898728044774316</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.002356611881832011</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.005440465988811501</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.002819962247127036</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.007721435553074058</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.007914170628509964</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.003179930828231455</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.003208451733199613</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.002387740203750831</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.005238778660923793</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.008664145651593458</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.004232428933551381</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01488033579843669</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.008544695960225442</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.02044434770775949</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.004652397486836435</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0003685858296445728</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0002066248833171672</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0001096473251454124</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0003005173106193524</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.000588571864284404</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7.465661324457698e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.00097722082921603</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0003845098335158085</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.001214353973154948</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0007321521265595266</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0001019804550736293</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0002688125899941163</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0001259142303510917</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0003985824476978211</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.000882835312069119</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.000166782513270347</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>175</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0003468126750118354</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0001540237347476771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0004257868150790058</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.001041900793524064</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0002201211713796491</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.005759844466925124</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.002381098171698026</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.006212064421058118</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001633186042226953</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0003612385029587703</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>250</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.00911097583472483</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.003266006395476365</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0106636879668713</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.002225964580574669</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0006022563219077357</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2855,4 +2856,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0002529962943561929</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0002280369184026793</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0004733621530626577</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001342842488156748</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0005251010336105627</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0002651040718002484</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0002282779446941976</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0004848386457286131</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001342916519433857</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0005250024256108387</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.000374778790518171</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0002335284023558042</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0008499960452040591</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001343018426041453</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0005247284793761648</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0005192698455148322</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0002859398625722052</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001490293798887954</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001343075651220715</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0005245328733588134</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.006065184866166806</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0021363113857991</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02033332778491249</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001343168706398501</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0005246336632257709</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0007120761068413936</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0004312443573446073</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.001192958999307175</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002603770637644942</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0005632724438154018</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.002772289312767517</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.001030899158386544</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.00423252735471318</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002602729105237955</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.000563432280685475</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0004847512758444268</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0002531303653497078</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0007683685152512445</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002602097596998476</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0005632841426032619</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0003197017643941831</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0002909708068404152</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0006042685395296817</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.00297443324606661</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0005660351889282593</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0005168812252174249</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0003788616976632703</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0008085439596702701</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.002971828052949377</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0005661330414118339</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3507,4 +3508,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.000178061542751499</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001758588452113622</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0002889124395513036</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0404309844961972</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.006494577377025575</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0003915386260818406</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0003170165069319181</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0008708651190439516</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.02020352141425974</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.003421112958328237</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.002067025236992315</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.001015596367871479</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.005254376057013226</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.004023137086846873</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001032569885361597</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0002480712350449998</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0002282642705739049</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0004265892257572894</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002774210367192609</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.000771608876052654</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0002214310373626442</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0002181770566923135</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0004176300620381912</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002558730198309433</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0005967861358016222</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0004592648313721526</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0002637107265231442</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.001071061879386476</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002581554612021364</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0005786538121590095</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0003398642711595438</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0003009588289080472</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.000619670793522406</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.00259981475331017</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0005649451222783478</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0004847512758444268</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0002531303653497078</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0007683685152512445</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002602097596998476</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0005632841426032619</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001067416281954762</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0004344953812663185</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.001630765430027493</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002603923353600379</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0005619642626836911</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0004760256123389854</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0003636588192024445</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0007773444258797554</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.002604151206764271</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0005618000795980368</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.000365346312973062</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0003198273953554976</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0006639157597779758</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.002604334426251853</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0005616683464707994</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0003614714386901419</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0003178474956317783</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.000659098948712416</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.002604357064885932</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0005616518909890227</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0003604470699397251</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0003169543587552097</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.000656721375969421</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.002604375261007874</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0005616388849839741</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4324,4 +4325,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0009298846374462914</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0003436092869541509</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0008248059666817361</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.004045373011199445</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.004074045411142885</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.001110373609373531</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0007087484857764373</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0008947104279761158</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.003665282787391311</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.00190744673478614</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001653754139098555</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001855080564203306</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0002850241876128186</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002956304807922527</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.00101276141730803</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0004527614641413417</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0004639106191511084</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.000645087481116903</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002477480792122289</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0006963275891410223</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0004847512758444268</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0002531303653497078</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0007683685152512445</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002602097596998476</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0005632841426032619</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.000219909696176875</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001717865439951164</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0006215369972492449</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001880673919485987</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0006872389317927159</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0002162194702178451</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.000184685566438482</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0004949285703061999</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001878282438783629</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0009948509774543588</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0002523077541115211</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001780642449505912</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0003682477143628232</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002909652024104536</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.001878024415172288</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0009298600596349497</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0003436026158620757</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0008247828764936715</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.004045373021886007</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.00407404545193473</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_7.xlsx
+++ b/Results/rbf_fd_parameter_study_7.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1166,4 +1167,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>890.2607527783233</v>
+      </c>
+      <c r="L2" t="n">
+        <v>429.9441507072957</v>
+      </c>
+      <c r="M2" t="n">
+        <v>175046.1411535962</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.007487533933757</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.0009488830607</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>238.960433820941</v>
+      </c>
+      <c r="L3" t="n">
+        <v>113.3184463829885</v>
+      </c>
+      <c r="M3" t="n">
+        <v>47406.58151685214</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.029950135921964</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.010952007942467</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.00136118698114777</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.001303667419364825</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.002899231163058074</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001998765487456922</v>
+      </c>
+      <c r="O4" t="n">
+        <v>9.470733992528665e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.003386325252158873</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.00290723925578205</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.006470170761873941</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.005000814690333755</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0002284857425690801</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.01163357828139751</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.009486964979173193</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02109462046052044</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.01700906729617202</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0007914762981531425</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.01793067049434175</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.01451650639817222</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.03226537511046382</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.02601505477836952</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.001218409102015999</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.02575492085259483</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.02076861393832397</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0461438976840827</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.03702212426254903</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.001746910606525644</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.03518920062426215</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02831099846688684</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.06287527279803003</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.05003013463667116</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.002384464945100501</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.04633777120130918</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.03722905767258897</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.08264217078738165</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.06503891941736129</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.003143805817406487</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.07429644651766276</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.05961507563979383</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1321926730256128</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1010579828403309</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.005102939189858615</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.1867465779616824</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1498885307098949</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3312137819673812</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.22610210913939</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01423593927843158</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.3993889017121314</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3211870252662334</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.7066564643804337</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.4011063083775923</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.03525260372681457</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>500</v>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.093804288372519</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.687529965786325</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.676461930139566</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.9007482170565169</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.155863854309355</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>500</v>
+      </c>
+      <c r="B15" t="n">
+        <v>500</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>151.6153659868391</v>
+      </c>
+      <c r="L15" t="n">
+        <v>123.2692837997967</v>
+      </c>
+      <c r="M15" t="n">
+        <v>288.6975359503887</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.599326011969964</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.4789448831979818</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>500</v>
+      </c>
+      <c r="B16" t="n">
+        <v>500</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.285381329517796</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.361157049197329</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.336556679131914</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.831981874191285</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.395598561445548</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>